--- a/public/lead_template.xlsx
+++ b/public/lead_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New_CRM\New_CRM_Bot\frontend\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41994156-A574-4D29-97E4-27C2F2EF6C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CF089C-0A2F-46FF-8540-7798F87F342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{B6FE3399-97C3-4DF9-8C31-9467B2187EB5}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{B6FE3399-97C3-4DF9-8C31-9467B2187EB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>company_name</t>
   </si>
@@ -51,12 +51,6 @@
     <t>assigned_to</t>
   </si>
   <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>turnover</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
@@ -67,13 +61,61 @@
   </si>
   <si>
     <t>lead_type</t>
+  </si>
+  <si>
+    <t>designation</t>
+  </si>
+  <si>
+    <t>company_email</t>
+  </si>
+  <si>
+    <t>company_phone_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">address </t>
+  </si>
+  <si>
+    <t xml:space="preserve">address_2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">city </t>
+  </si>
+  <si>
+    <t xml:space="preserve">state </t>
+  </si>
+  <si>
+    <t>pincode</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turnover </t>
+  </si>
+  <si>
+    <t xml:space="preserve">team_size </t>
+  </si>
+  <si>
+    <t xml:space="preserve">segment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">current_system </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remark </t>
+  </si>
+  <si>
+    <t xml:space="preserve">activity_type </t>
+  </si>
+  <si>
+    <t>activity_details</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +127,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -107,14 +163,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -427,14 +486,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6500658-1A72-4ADD-9D32-C08491763852}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="7.44140625" customWidth="1"/>
+    <col min="20" max="20" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -445,31 +511,82 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/lead_template.xlsx
+++ b/public/lead_template.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CF089C-0A2F-46FF-8540-7798F87F342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{B6FE3399-97C3-4DF9-8C31-9467B2187EB5}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11715" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>company_name</t>
   </si>
@@ -109,13 +103,37 @@
   </si>
   <si>
     <t>activity_details</t>
+  </si>
+  <si>
+    <t>verticles</t>
+  </si>
+  <si>
+    <t>opportunity_bussiness</t>
+  </si>
+  <si>
+    <t>target_closing_date</t>
+  </si>
+  <si>
+    <t>gst</t>
+  </si>
+  <si>
+    <t>company_pan</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>database_type</t>
+  </si>
+  <si>
+    <t>amc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,7 +250,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -284,7 +302,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -478,29 +496,49 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6500658-1A72-4ADD-9D32-C08491763852}">
-  <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AG3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="7.44140625" customWidth="1"/>
-    <col min="20" max="20" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,17 +609,41 @@
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33">
       <c r="B2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33">
       <c r="B3" s="2"/>
       <c r="F3" s="2"/>
     </row>
